--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K557"/>
+  <dimension ref="A1:K559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22101,6 +22101,84 @@
         <v>397.69</v>
       </c>
       <c r="K557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>442.92</v>
+      </c>
+      <c r="C558" t="n">
+        <v>464.68</v>
+      </c>
+      <c r="D558" t="n">
+        <v>390.52</v>
+      </c>
+      <c r="E558" t="n">
+        <v>393.18</v>
+      </c>
+      <c r="F558" t="n">
+        <v>393.7</v>
+      </c>
+      <c r="G558" t="n">
+        <v>387.65</v>
+      </c>
+      <c r="H558" t="n">
+        <v>388.39</v>
+      </c>
+      <c r="I558" t="n">
+        <v>392.23</v>
+      </c>
+      <c r="J558" t="n">
+        <v>399</v>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>447.25</v>
+      </c>
+      <c r="C559" t="n">
+        <v>471.88</v>
+      </c>
+      <c r="D559" t="n">
+        <v>395.3</v>
+      </c>
+      <c r="E559" t="n">
+        <v>397.46</v>
+      </c>
+      <c r="F559" t="n">
+        <v>397.07</v>
+      </c>
+      <c r="G559" t="n">
+        <v>390.36</v>
+      </c>
+      <c r="H559" t="n">
+        <v>390.53</v>
+      </c>
+      <c r="I559" t="n">
+        <v>394.62</v>
+      </c>
+      <c r="J559" t="n">
+        <v>401.17</v>
+      </c>
+      <c r="K559" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22117,7 +22195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27790,6 +27868,26 @@
       </c>
       <c r="B567" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -27958,28 +28056,28 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05612627853402152</v>
+        <v>0.06114572823929376</v>
       </c>
       <c r="J2" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000504920026753064</v>
+        <v>0.0006035582691960029</v>
       </c>
       <c r="M2" t="n">
-        <v>13.91701055946018</v>
+        <v>13.9023672520726</v>
       </c>
       <c r="N2" t="n">
-        <v>336.647814019727</v>
+        <v>335.6238569835852</v>
       </c>
       <c r="O2" t="n">
-        <v>18.34796484680868</v>
+        <v>18.32003976479269</v>
       </c>
       <c r="P2" t="n">
-        <v>436.6189337704969</v>
+        <v>436.5663559984339</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28040,28 +28138,28 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2236325027644182</v>
+        <v>-0.2070606229048908</v>
       </c>
       <c r="J3" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K3" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003697075795464855</v>
+        <v>0.00318780485283332</v>
       </c>
       <c r="M3" t="n">
-        <v>22.10530231236142</v>
+        <v>22.10896184266901</v>
       </c>
       <c r="N3" t="n">
-        <v>699.1984011277</v>
+        <v>698.4714423031122</v>
       </c>
       <c r="O3" t="n">
-        <v>26.44235997651685</v>
+        <v>26.42861029837006</v>
       </c>
       <c r="P3" t="n">
-        <v>451.9162157989588</v>
+        <v>451.7372092973877</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28122,28 +28220,28 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1886563437765931</v>
+        <v>-0.1907749034396949</v>
       </c>
       <c r="J4" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K4" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0138895775942165</v>
+        <v>0.01430335603601107</v>
       </c>
       <c r="M4" t="n">
-        <v>9.390911489192433</v>
+        <v>9.368704970684629</v>
       </c>
       <c r="N4" t="n">
-        <v>135.5492296930951</v>
+        <v>135.1113563007411</v>
       </c>
       <c r="O4" t="n">
-        <v>11.64256113117277</v>
+        <v>11.62374106304597</v>
       </c>
       <c r="P4" t="n">
-        <v>400.8055013586546</v>
+        <v>400.8277804089523</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28204,28 +28302,28 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4956653295605085</v>
+        <v>-0.5007750103572179</v>
       </c>
       <c r="J5" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K5" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2130042389141559</v>
+        <v>0.2171128238742495</v>
       </c>
       <c r="M5" t="n">
-        <v>5.048491468542517</v>
+        <v>5.05612582590317</v>
       </c>
       <c r="N5" t="n">
-        <v>48.56078137673069</v>
+        <v>48.58102739949566</v>
       </c>
       <c r="O5" t="n">
-        <v>6.968556620759474</v>
+        <v>6.970009139125692</v>
       </c>
       <c r="P5" t="n">
-        <v>415.4336109144567</v>
+        <v>415.4873390496227</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28286,28 +28384,28 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5097993231293336</v>
+        <v>-0.5154807349832865</v>
       </c>
       <c r="J6" t="n">
+        <v>558</v>
+      </c>
+      <c r="K6" t="n">
         <v>556</v>
       </c>
-      <c r="K6" t="n">
-        <v>554</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.2789326696388121</v>
+        <v>0.2836916890584172</v>
       </c>
       <c r="M6" t="n">
-        <v>4.883542460336108</v>
+        <v>4.892460283945226</v>
       </c>
       <c r="N6" t="n">
-        <v>36.28505444557391</v>
+        <v>36.38798981559938</v>
       </c>
       <c r="O6" t="n">
-        <v>6.023707699214323</v>
+        <v>6.032245835142943</v>
       </c>
       <c r="P6" t="n">
-        <v>416.7087817156873</v>
+        <v>416.7681917765395</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -28368,28 +28466,28 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4915416080868892</v>
+        <v>-0.4964668810621646</v>
       </c>
       <c r="J7" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K7" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2841334837374209</v>
+        <v>0.2887229357696933</v>
       </c>
       <c r="M7" t="n">
-        <v>4.493060981261512</v>
+        <v>4.501292557675547</v>
       </c>
       <c r="N7" t="n">
-        <v>32.76773435905489</v>
+        <v>32.82393570509765</v>
       </c>
       <c r="O7" t="n">
-        <v>5.724310819570762</v>
+        <v>5.729217721914367</v>
       </c>
       <c r="P7" t="n">
-        <v>408.7865889221015</v>
+        <v>408.8381528430689</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -28450,28 +28548,28 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3090178758340522</v>
+        <v>-0.3121331410870062</v>
       </c>
       <c r="J8" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K8" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1327528729769607</v>
+        <v>0.1357471368950653</v>
       </c>
       <c r="M8" t="n">
-        <v>4.479634282238997</v>
+        <v>4.475476789485286</v>
       </c>
       <c r="N8" t="n">
-        <v>33.58012869028848</v>
+        <v>33.53068942551632</v>
       </c>
       <c r="O8" t="n">
-        <v>5.79483638166674</v>
+        <v>5.790569007059351</v>
       </c>
       <c r="P8" t="n">
-        <v>401.9256040871449</v>
+        <v>401.9582184870185</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -28532,28 +28630,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1395310856272728</v>
+        <v>-0.1431727395097215</v>
       </c>
       <c r="J9" t="n">
+        <v>558</v>
+      </c>
+      <c r="K9" t="n">
         <v>556</v>
       </c>
-      <c r="K9" t="n">
-        <v>554</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0258887106052661</v>
+        <v>0.0273625685396367</v>
       </c>
       <c r="M9" t="n">
-        <v>4.935340054720292</v>
+        <v>4.936554999522829</v>
       </c>
       <c r="N9" t="n">
-        <v>39.5532393041731</v>
+        <v>39.50780077494936</v>
       </c>
       <c r="O9" t="n">
-        <v>6.28913661039201</v>
+        <v>6.285523110684532</v>
       </c>
       <c r="P9" t="n">
-        <v>402.1703351827234</v>
+        <v>402.2084256911326</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -28614,28 +28712,28 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03777624006009785</v>
+        <v>0.03464718930963754</v>
       </c>
       <c r="J10" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K10" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002776837274633182</v>
+        <v>0.002349007117155022</v>
       </c>
       <c r="M10" t="n">
-        <v>4.215383158367817</v>
+        <v>4.216735108394703</v>
       </c>
       <c r="N10" t="n">
-        <v>27.6949434156794</v>
+        <v>27.66696724895402</v>
       </c>
       <c r="O10" t="n">
-        <v>5.262598542134808</v>
+        <v>5.259939852218276</v>
       </c>
       <c r="P10" t="n">
-        <v>403.4502666403675</v>
+        <v>403.4830435302376</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -28677,7 +28775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K557"/>
+  <dimension ref="A1:K559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60297,6 +60395,120 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-36.52819287083712,174.71520656212505</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-36.52892387774441,174.71538946488513</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-36.52963026753416,174.71450076838855</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-36.530357903103436,174.71431482345014</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-36.531042779104716,174.7141076555676</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-36.53174186328333,174.71392196409087</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-36.53246039750112,174.7137605877941</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-36.53315332166494,174.7136216687095</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-36.53384628818397,174.71365790971242</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-36.528195010765835,174.71525484289228</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-36.5289274358914,174.71546974775458</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-36.5296362767057,174.71455362624363</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-36.53036664150642,174.71436137736345</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-36.53104812770221,174.71414470192093</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-36.531745500122426,174.713951890916</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-36.5324639548405,174.71378407666887</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-36.53315578960288,174.7136481840147</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-36.533846957813864,174.71368212987588</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K559"/>
+  <dimension ref="A1:K561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22179,6 +22179,84 @@
         <v>401.17</v>
       </c>
       <c r="K559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>448.65</v>
+      </c>
+      <c r="C560" t="n">
+        <v>480.49</v>
+      </c>
+      <c r="D560" t="n">
+        <v>391.13</v>
+      </c>
+      <c r="E560" t="n">
+        <v>395.01</v>
+      </c>
+      <c r="F560" t="n">
+        <v>396.17</v>
+      </c>
+      <c r="G560" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="H560" t="n">
+        <v>389.9</v>
+      </c>
+      <c r="I560" t="n">
+        <v>393.97</v>
+      </c>
+      <c r="J560" t="n">
+        <v>400.24</v>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>448.78</v>
+      </c>
+      <c r="C561" t="n">
+        <v>480.49</v>
+      </c>
+      <c r="D561" t="n">
+        <v>392.23</v>
+      </c>
+      <c r="E561" t="n">
+        <v>396.56</v>
+      </c>
+      <c r="F561" t="n">
+        <v>397.06</v>
+      </c>
+      <c r="G561" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="H561" t="n">
+        <v>390.21</v>
+      </c>
+      <c r="I561" t="n">
+        <v>394.32</v>
+      </c>
+      <c r="J561" t="n">
+        <v>400.72</v>
+      </c>
+      <c r="K561" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22195,7 +22273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B569"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27888,6 +27966,26 @@
       </c>
       <c r="B569" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -28056,28 +28154,28 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06114572823929376</v>
+        <v>0.06868081140752755</v>
       </c>
       <c r="J2" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K2" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006035582691960029</v>
+        <v>0.000766407564951499</v>
       </c>
       <c r="M2" t="n">
-        <v>13.9023672520726</v>
+        <v>13.9053217350504</v>
       </c>
       <c r="N2" t="n">
-        <v>335.6238569835852</v>
+        <v>334.8115676456327</v>
       </c>
       <c r="O2" t="n">
-        <v>18.32003976479269</v>
+        <v>18.29785691401134</v>
       </c>
       <c r="P2" t="n">
-        <v>436.5663559984339</v>
+        <v>436.4871565046408</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28138,28 +28236,28 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2070606229048908</v>
+        <v>-0.1816790063735158</v>
       </c>
       <c r="J3" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K3" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00318780485283332</v>
+        <v>0.002460466369431424</v>
       </c>
       <c r="M3" t="n">
-        <v>22.10896184266901</v>
+        <v>22.15675284751577</v>
       </c>
       <c r="N3" t="n">
-        <v>698.4714423031122</v>
+        <v>700.1526647468792</v>
       </c>
       <c r="O3" t="n">
-        <v>26.42861029837006</v>
+        <v>26.46039804588886</v>
       </c>
       <c r="P3" t="n">
-        <v>451.7372092973877</v>
+        <v>451.4621222373592</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28220,28 +28318,28 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1907749034396949</v>
+        <v>-0.1937316024319323</v>
       </c>
       <c r="J4" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01430335603601107</v>
+        <v>0.01485087789816408</v>
       </c>
       <c r="M4" t="n">
-        <v>9.368704970684629</v>
+        <v>9.351156080218653</v>
       </c>
       <c r="N4" t="n">
-        <v>135.1113563007411</v>
+        <v>134.6867281483413</v>
       </c>
       <c r="O4" t="n">
-        <v>11.62374106304597</v>
+        <v>11.60546113467023</v>
       </c>
       <c r="P4" t="n">
-        <v>400.8277804089523</v>
+        <v>400.8589794652091</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28302,28 +28400,28 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5007750103572179</v>
+        <v>-0.5054435089437351</v>
       </c>
       <c r="J5" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K5" t="n">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2171128238742495</v>
+        <v>0.2210935627781991</v>
       </c>
       <c r="M5" t="n">
-        <v>5.05612582590317</v>
+        <v>5.061596335987869</v>
       </c>
       <c r="N5" t="n">
-        <v>48.58102739949566</v>
+        <v>48.55890900958005</v>
       </c>
       <c r="O5" t="n">
-        <v>6.970009139125692</v>
+        <v>6.968422275492498</v>
       </c>
       <c r="P5" t="n">
-        <v>415.4873390496227</v>
+        <v>415.5365930824623</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28384,28 +28482,28 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5154807349832865</v>
+        <v>-0.5201662652597235</v>
       </c>
       <c r="J6" t="n">
+        <v>560</v>
+      </c>
+      <c r="K6" t="n">
         <v>558</v>
       </c>
-      <c r="K6" t="n">
-        <v>556</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.2836916890584172</v>
+        <v>0.2881184159265044</v>
       </c>
       <c r="M6" t="n">
-        <v>4.892460283945226</v>
+        <v>4.896626696573517</v>
       </c>
       <c r="N6" t="n">
-        <v>36.38798981559938</v>
+        <v>36.41090001208342</v>
       </c>
       <c r="O6" t="n">
-        <v>6.032245835142943</v>
+        <v>6.03414451368903</v>
       </c>
       <c r="P6" t="n">
-        <v>416.7681917765395</v>
+        <v>416.8173554295497</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -28466,28 +28564,28 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4964668810621646</v>
+        <v>-0.5001660647949112</v>
       </c>
       <c r="J7" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K7" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2887229357696933</v>
+        <v>0.2927931613927677</v>
       </c>
       <c r="M7" t="n">
-        <v>4.501292557675547</v>
+        <v>4.503463447926676</v>
       </c>
       <c r="N7" t="n">
-        <v>32.82393570509765</v>
+        <v>32.80245894744068</v>
       </c>
       <c r="O7" t="n">
-        <v>5.729217721914367</v>
+        <v>5.727343096710785</v>
       </c>
       <c r="P7" t="n">
-        <v>408.8381528430689</v>
+        <v>408.8770114009694</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -28548,28 +28646,28 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3121331410870062</v>
+        <v>-0.3147580818480425</v>
       </c>
       <c r="J8" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K8" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1357471368950653</v>
+        <v>0.1384842143598126</v>
       </c>
       <c r="M8" t="n">
-        <v>4.475476789485286</v>
+        <v>4.46948653930263</v>
       </c>
       <c r="N8" t="n">
-        <v>33.53068942551632</v>
+        <v>33.45870910360355</v>
       </c>
       <c r="O8" t="n">
-        <v>5.790569007059351</v>
+        <v>5.784350361415148</v>
       </c>
       <c r="P8" t="n">
-        <v>401.9582184870185</v>
+        <v>401.9857933356841</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -28630,28 +28728,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1431727395097215</v>
+        <v>-0.1462357024055936</v>
       </c>
       <c r="J9" t="n">
+        <v>560</v>
+      </c>
+      <c r="K9" t="n">
         <v>558</v>
       </c>
-      <c r="K9" t="n">
-        <v>556</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0273625685396367</v>
+        <v>0.02868283329627486</v>
       </c>
       <c r="M9" t="n">
-        <v>4.936554999522829</v>
+        <v>4.934685406510282</v>
       </c>
       <c r="N9" t="n">
-        <v>39.50780077494936</v>
+        <v>39.43152486348382</v>
       </c>
       <c r="O9" t="n">
-        <v>6.285523110684532</v>
+        <v>6.279452592661547</v>
       </c>
       <c r="P9" t="n">
-        <v>402.2084256911326</v>
+        <v>402.2405732185076</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -28712,28 +28810,28 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03464718930963754</v>
+        <v>0.03184762252724916</v>
       </c>
       <c r="J10" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K10" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002349007117155022</v>
+        <v>0.001996981576106505</v>
       </c>
       <c r="M10" t="n">
-        <v>4.216735108394703</v>
+        <v>4.216328877507002</v>
       </c>
       <c r="N10" t="n">
-        <v>27.66696724895402</v>
+        <v>27.62211299268686</v>
       </c>
       <c r="O10" t="n">
-        <v>5.259939852218276</v>
+        <v>5.255674361362855</v>
       </c>
       <c r="P10" t="n">
-        <v>403.4830435302376</v>
+        <v>403.5124700788019</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -28775,7 +28873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K559"/>
+  <dimension ref="A1:K561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60509,6 +60607,120 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-36.52819570265543,174.7152704533024</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-36.528931690770946,174.71556575269278</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-36.52963103439628,174.71450751384663</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-36.53036163938548,174.71433472851</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-36.53104669929451,174.71413480823563</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-36.53174507068056,174.71394835712104</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-36.532462907586854,174.71377716171955</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-36.533155118406945,174.7136409727391</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>-36.53384667083023,174.7136717498058</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-36.528195766902215,174.71527190284047</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-36.528931690770946,174.71556575269278</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-36.529632417261425,174.71451967778776</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-36.53036480399331,174.71435158798832</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-36.531048111831,174.7141445919911</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-36.53174649320632,174.71396006281702</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-36.5324634229022,174.71378056431362</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-36.5331554798202,174.71364485573363</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>-36.53384681895092,174.7136771072613</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K561"/>
+  <dimension ref="A1:K562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22233,7 +22233,7 @@
         <v>448.78</v>
       </c>
       <c r="C561" t="n">
-        <v>480.49</v>
+        <v>475.73</v>
       </c>
       <c r="D561" t="n">
         <v>392.23</v>
@@ -22259,6 +22259,45 @@
       <c r="K561" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>452.3</v>
+      </c>
+      <c r="C562" t="n">
+        <v>468.66</v>
+      </c>
+      <c r="D562" t="n">
+        <v>390.96</v>
+      </c>
+      <c r="E562" t="n">
+        <v>397.37</v>
+      </c>
+      <c r="F562" t="n">
+        <v>398.64</v>
+      </c>
+      <c r="G562" t="n">
+        <v>393.44</v>
+      </c>
+      <c r="H562" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="I562" t="n">
+        <v>393.51</v>
+      </c>
+      <c r="J562" t="n">
+        <v>400.34</v>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -22273,7 +22312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27986,6 +28025,16 @@
       </c>
       <c r="B571" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -28154,34 +28203,30 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06868081140752755</v>
+        <v>0.07371087020210666</v>
       </c>
       <c r="J2" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K2" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000766407564951499</v>
+        <v>0.0008852327751388556</v>
       </c>
       <c r="M2" t="n">
-        <v>13.9053217350504</v>
+        <v>13.91535716784056</v>
       </c>
       <c r="N2" t="n">
-        <v>334.8115676456327</v>
+        <v>334.5601109708419</v>
       </c>
       <c r="O2" t="n">
-        <v>18.29785691401134</v>
+        <v>18.29098441776281</v>
       </c>
       <c r="P2" t="n">
-        <v>436.4871565046408</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>436.4340082643617</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.7102678844082 -36.52797387172354, 174.72054548935918 -36.5284293865141)</t>
@@ -28236,34 +28281,30 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1816790063735158</v>
+        <v>-0.1752235910206716</v>
       </c>
       <c r="J3" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K3" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002460466369431424</v>
+        <v>0.002297163937180269</v>
       </c>
       <c r="M3" t="n">
-        <v>22.15675284751577</v>
+        <v>22.14846215028491</v>
       </c>
       <c r="N3" t="n">
-        <v>700.1526647468792</v>
+        <v>699.2069452788708</v>
       </c>
       <c r="O3" t="n">
-        <v>26.46039804588886</v>
+        <v>26.44252153783506</v>
       </c>
       <c r="P3" t="n">
-        <v>451.4621222373592</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>451.3917094390553</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.7102081086602 -36.52869412412259, 174.72048577572545 -36.52914963882)</t>
@@ -28318,34 +28359,30 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1937316024319323</v>
+        <v>-0.1954525298013798</v>
       </c>
       <c r="J4" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K4" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01485087789816408</v>
+        <v>0.01516630635292127</v>
       </c>
       <c r="M4" t="n">
-        <v>9.351156080218653</v>
+        <v>9.343649706760802</v>
       </c>
       <c r="N4" t="n">
-        <v>134.6867281483413</v>
+        <v>134.4854733157613</v>
       </c>
       <c r="O4" t="n">
-        <v>11.60546113467023</v>
+        <v>11.59678719800279</v>
       </c>
       <c r="P4" t="n">
-        <v>400.8589794652091</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>400.8772349036824</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.71018237249172 -36.529139245836106, 174.720374709976 -36.53029789968069)</t>
@@ -28400,34 +28437,30 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5054435089437351</v>
+        <v>-0.5071697745341899</v>
       </c>
       <c r="J5" t="n">
+        <v>561</v>
+      </c>
+      <c r="K5" t="n">
         <v>560</v>
       </c>
-      <c r="K5" t="n">
-        <v>559</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2210935627781991</v>
+        <v>0.2228105940408112</v>
       </c>
       <c r="M5" t="n">
-        <v>5.061596335987869</v>
+        <v>5.061151292934885</v>
       </c>
       <c r="N5" t="n">
-        <v>48.55890900958005</v>
+        <v>48.51279435195639</v>
       </c>
       <c r="O5" t="n">
-        <v>6.968422275492498</v>
+        <v>6.965112658956522</v>
       </c>
       <c r="P5" t="n">
-        <v>415.5365930824623</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>415.554901344612</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.71003821387956 -36.52955507542649, 174.72006316250176 -36.53143674162229)</t>
@@ -28482,34 +28515,30 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5201662652597235</v>
+        <v>-0.5217446566655847</v>
       </c>
       <c r="J6" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K6" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2881184159265044</v>
+        <v>0.2899800094024173</v>
       </c>
       <c r="M6" t="n">
-        <v>4.896626696573517</v>
+        <v>4.895131370315577</v>
       </c>
       <c r="N6" t="n">
-        <v>36.41090001208342</v>
+        <v>36.38016300242726</v>
       </c>
       <c r="O6" t="n">
-        <v>6.03414451368903</v>
+        <v>6.031597052392281</v>
       </c>
       <c r="P6" t="n">
-        <v>416.8173554295497</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>416.8340044944439</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.709779750126 -36.5304178494028, 174.7199117999006 -36.53188060688336)</t>
@@ -28564,34 +28593,30 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5001660647949112</v>
+        <v>-0.5009513256836639</v>
       </c>
       <c r="J7" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K7" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2927931613927677</v>
+        <v>0.2942090712654661</v>
       </c>
       <c r="M7" t="n">
-        <v>4.503463447926676</v>
+        <v>4.499282036753705</v>
       </c>
       <c r="N7" t="n">
-        <v>32.80245894744068</v>
+        <v>32.75246457301743</v>
       </c>
       <c r="O7" t="n">
-        <v>5.727343096710785</v>
+        <v>5.722976897823145</v>
       </c>
       <c r="P7" t="n">
-        <v>408.8770114009694</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>408.8853037699531</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.70964112876095 -36.531221556064544, 174.71981948455283 -36.5324584033383)</t>
@@ -28646,34 +28671,30 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3147580818480425</v>
+        <v>-0.3159968283471656</v>
       </c>
       <c r="J8" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K8" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1384842143598126</v>
+        <v>0.1398227246602612</v>
       </c>
       <c r="M8" t="n">
-        <v>4.46948653930263</v>
+        <v>4.466250007156045</v>
       </c>
       <c r="N8" t="n">
-        <v>33.45870910360355</v>
+        <v>33.42016297082246</v>
       </c>
       <c r="O8" t="n">
-        <v>5.784350361415148</v>
+        <v>5.78101746847581</v>
       </c>
       <c r="P8" t="n">
-        <v>401.9857933356841</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>401.9988745207973</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.70949760921704 -36.531814696029414, 174.71961399811005 -36.53334672966315)</t>
@@ -28728,34 +28749,30 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1462357024055936</v>
+        <v>-0.1479800477516861</v>
       </c>
       <c r="J9" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K9" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02868283329627486</v>
+        <v>0.02943307676946805</v>
       </c>
       <c r="M9" t="n">
-        <v>4.934685406510282</v>
+        <v>4.934749749666248</v>
       </c>
       <c r="N9" t="n">
-        <v>39.43152486348382</v>
+        <v>39.40299717860527</v>
       </c>
       <c r="O9" t="n">
-        <v>6.279452592661547</v>
+        <v>6.277180671177568</v>
       </c>
       <c r="P9" t="n">
-        <v>402.2405732185076</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>402.2589776543526</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.70927018286895 -36.53274822051205, 174.71949576736307 -36.533699910643975)</t>
@@ -28810,34 +28827,30 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03184762252724916</v>
+        <v>0.03040485777179393</v>
       </c>
       <c r="J10" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K10" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001996981576106505</v>
+        <v>0.001825728012630035</v>
       </c>
       <c r="M10" t="n">
-        <v>4.216328877507002</v>
+        <v>4.216355447322053</v>
       </c>
       <c r="N10" t="n">
-        <v>27.62211299268686</v>
+        <v>27.6012572510045</v>
       </c>
       <c r="O10" t="n">
-        <v>5.255674361362855</v>
+        <v>5.253689870082217</v>
       </c>
       <c r="P10" t="n">
-        <v>403.5124700788019</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>403.5277157289366</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (174.70920452856095 -36.53372307885477, 174.7194921095911 -36.5340074472448)</t>
@@ -28873,7 +28886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K561"/>
+  <dimension ref="A1:K562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60677,7 +60690,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>-36.528931690770946,174.71556575269278</t>
+          <t>-36.528929338489405,174.7155126767911</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -60718,6 +60731,63 @@
       <c r="K561" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-36.528197506500845,174.71531115187256</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-36.528925844615706,174.71543384347066</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-36.52963082068065,174.71450563396485</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-36.530366457755136,174.7143603984259</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-36.53105061947807,174.71416196090615</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-36.5317496334949,174.7139859036945</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-36.53246340627912,174.71378045455253</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-36.5331546434065,174.71363586937488</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-36.533846701688724,174.71367286594236</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -22116,7 +22116,7 @@
         <v>442.92</v>
       </c>
       <c r="C558" t="n">
-        <v>464.68</v>
+        <v>455.1</v>
       </c>
       <c r="D558" t="n">
         <v>390.52</v>
@@ -22155,7 +22155,7 @@
         <v>447.25</v>
       </c>
       <c r="C559" t="n">
-        <v>471.88</v>
+        <v>455.1</v>
       </c>
       <c r="D559" t="n">
         <v>395.3</v>
@@ -22194,7 +22194,7 @@
         <v>448.65</v>
       </c>
       <c r="C560" t="n">
-        <v>480.49</v>
+        <v>455.67</v>
       </c>
       <c r="D560" t="n">
         <v>391.13</v>
@@ -22233,7 +22233,7 @@
         <v>448.78</v>
       </c>
       <c r="C561" t="n">
-        <v>475.73</v>
+        <v>455.67</v>
       </c>
       <c r="D561" t="n">
         <v>392.23</v>
@@ -22272,7 +22272,7 @@
         <v>452.3</v>
       </c>
       <c r="C562" t="n">
-        <v>468.66</v>
+        <v>439.17</v>
       </c>
       <c r="D562" t="n">
         <v>390.96</v>
@@ -22312,7 +22312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B572"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28035,6 +28035,16 @@
       </c>
       <c r="B572" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -28281,7 +28291,7 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1752235910206716</v>
+        <v>-0.2124300581200867</v>
       </c>
       <c r="J3" t="n">
         <v>561</v>
@@ -28290,19 +28300,19 @@
         <v>546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002297163937180269</v>
+        <v>0.003400241211841903</v>
       </c>
       <c r="M3" t="n">
-        <v>22.14846215028491</v>
+        <v>21.98570615527224</v>
       </c>
       <c r="N3" t="n">
-        <v>699.2069452788708</v>
+        <v>693.512591041283</v>
       </c>
       <c r="O3" t="n">
-        <v>26.44252153783506</v>
+        <v>26.33462722427039</v>
       </c>
       <c r="P3" t="n">
-        <v>451.3917094390553</v>
+        <v>451.7951947367942</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -60519,7 +60529,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>-36.52892387774441,174.71538946488513</t>
+          <t>-36.528919143348,174.7152826440752</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -60576,7 +60586,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>-36.5289274358914,174.71546974775458</t>
+          <t>-36.528919143348,174.7152826440752</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -60633,7 +60643,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>-36.528931690770946,174.71556575269278</t>
+          <t>-36.52891942504234,174.71528899980163</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -60690,7 +60700,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>-36.528929338489405,174.7155126767911</t>
+          <t>-36.52891942504234,174.71528899980163</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -60747,7 +60757,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>-36.528925844615706,174.71543384347066</t>
+          <t>-36.52891127059514,174.71510501826018</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">

--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K562"/>
+  <dimension ref="A1:K566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22298,6 +22298,162 @@
       <c r="K562" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>452.82</v>
+      </c>
+      <c r="C563" t="n">
+        <v>455.79</v>
+      </c>
+      <c r="D563" t="n">
+        <v>390.22</v>
+      </c>
+      <c r="E563" t="n">
+        <v>396.97</v>
+      </c>
+      <c r="F563" t="n">
+        <v>399.2</v>
+      </c>
+      <c r="G563" t="n">
+        <v>393.64</v>
+      </c>
+      <c r="H563" t="n">
+        <v>390.9</v>
+      </c>
+      <c r="I563" t="n">
+        <v>393.42</v>
+      </c>
+      <c r="J563" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>455.42</v>
+      </c>
+      <c r="C564" t="n">
+        <v>463.19</v>
+      </c>
+      <c r="D564" t="n">
+        <v>395.32</v>
+      </c>
+      <c r="E564" t="n">
+        <v>401.41</v>
+      </c>
+      <c r="F564" t="n">
+        <v>400.99</v>
+      </c>
+      <c r="G564" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="H564" t="n">
+        <v>392.34</v>
+      </c>
+      <c r="I564" t="n">
+        <v>393.72</v>
+      </c>
+      <c r="J564" t="n">
+        <v>400.28</v>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>461.36</v>
+      </c>
+      <c r="C565" t="n">
+        <v>470.09</v>
+      </c>
+      <c r="D565" t="n">
+        <v>394.91</v>
+      </c>
+      <c r="E565" t="n">
+        <v>399.11</v>
+      </c>
+      <c r="F565" t="n">
+        <v>399.43</v>
+      </c>
+      <c r="G565" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="H565" t="n">
+        <v>394.85</v>
+      </c>
+      <c r="I565" t="n">
+        <v>394.65</v>
+      </c>
+      <c r="J565" t="n">
+        <v>400.82</v>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>462.57</v>
+      </c>
+      <c r="C566" t="n">
+        <v>475.89</v>
+      </c>
+      <c r="D566" t="n">
+        <v>398.46</v>
+      </c>
+      <c r="E566" t="n">
+        <v>401.31</v>
+      </c>
+      <c r="F566" t="n">
+        <v>399.06</v>
+      </c>
+      <c r="G566" t="n">
+        <v>395.92</v>
+      </c>
+      <c r="H566" t="n">
+        <v>394.54</v>
+      </c>
+      <c r="I566" t="n">
+        <v>393.97</v>
+      </c>
+      <c r="J566" t="n">
+        <v>400.68</v>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28045,6 +28201,36 @@
       </c>
       <c r="B573" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -28213,28 +28399,28 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07371087020210666</v>
+        <v>0.1015783243734737</v>
       </c>
       <c r="J2" t="n">
+        <v>565</v>
+      </c>
+      <c r="K2" t="n">
         <v>561</v>
       </c>
-      <c r="K2" t="n">
-        <v>557</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0008852327751388556</v>
+        <v>0.001692084280673245</v>
       </c>
       <c r="M2" t="n">
-        <v>13.91535716784056</v>
+        <v>14.00795935843887</v>
       </c>
       <c r="N2" t="n">
-        <v>334.5601109708419</v>
+        <v>334.9822609021711</v>
       </c>
       <c r="O2" t="n">
-        <v>18.29098441776281</v>
+        <v>18.30252061608376</v>
       </c>
       <c r="P2" t="n">
-        <v>436.4340082643617</v>
+        <v>436.1382721020239</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28291,28 +28477,28 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2124300581200867</v>
+        <v>-0.1828378496938012</v>
       </c>
       <c r="J3" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="K3" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003400241211841903</v>
+        <v>0.002549474661560747</v>
       </c>
       <c r="M3" t="n">
-        <v>21.98570615527224</v>
+        <v>21.97337336669043</v>
       </c>
       <c r="N3" t="n">
-        <v>693.512591041283</v>
+        <v>691.7495630941373</v>
       </c>
       <c r="O3" t="n">
-        <v>26.33462722427039</v>
+        <v>26.30113235383863</v>
       </c>
       <c r="P3" t="n">
-        <v>451.7951947367942</v>
+        <v>451.4713385666681</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28369,28 +28555,28 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1954525298013798</v>
+        <v>-0.1967970856419625</v>
       </c>
       <c r="J4" t="n">
+        <v>565</v>
+      </c>
+      <c r="K4" t="n">
         <v>561</v>
       </c>
-      <c r="K4" t="n">
-        <v>557</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01516630635292127</v>
+        <v>0.01560519556790774</v>
       </c>
       <c r="M4" t="n">
-        <v>9.343649706760802</v>
+        <v>9.294279449063971</v>
       </c>
       <c r="N4" t="n">
-        <v>134.4854733157613</v>
+        <v>133.5951332159486</v>
       </c>
       <c r="O4" t="n">
-        <v>11.59678719800279</v>
+        <v>11.55833609201379</v>
       </c>
       <c r="P4" t="n">
-        <v>400.8772349036824</v>
+        <v>400.8914648898224</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28447,28 +28633,28 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5071697745341899</v>
+        <v>-0.5105414161616315</v>
       </c>
       <c r="J5" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="K5" t="n">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2228105940408112</v>
+        <v>0.2276537260324583</v>
       </c>
       <c r="M5" t="n">
-        <v>5.061151292934885</v>
+        <v>5.041819749947176</v>
       </c>
       <c r="N5" t="n">
-        <v>48.51279435195639</v>
+        <v>48.23190217618323</v>
       </c>
       <c r="O5" t="n">
-        <v>6.965112658956522</v>
+        <v>6.944919162681682</v>
       </c>
       <c r="P5" t="n">
-        <v>415.554901344612</v>
+        <v>415.5907557105127</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28525,28 +28711,28 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5217446566655847</v>
+        <v>-0.5264140901197916</v>
       </c>
       <c r="J6" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="K6" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2899800094024173</v>
+        <v>0.2964796235121451</v>
       </c>
       <c r="M6" t="n">
-        <v>4.895131370315577</v>
+        <v>4.881503328796901</v>
       </c>
       <c r="N6" t="n">
-        <v>36.38016300242726</v>
+        <v>36.20150234577441</v>
       </c>
       <c r="O6" t="n">
-        <v>6.031597052392281</v>
+        <v>6.016768430459527</v>
       </c>
       <c r="P6" t="n">
-        <v>416.8340044944439</v>
+        <v>416.8834551540934</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28603,28 +28789,28 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5009513256836639</v>
+        <v>-0.5011568753536099</v>
       </c>
       <c r="J7" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="K7" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2942090712654661</v>
+        <v>0.2976138032355655</v>
       </c>
       <c r="M7" t="n">
-        <v>4.499282036753705</v>
+        <v>4.473332549692815</v>
       </c>
       <c r="N7" t="n">
-        <v>32.75246457301743</v>
+        <v>32.52861137064205</v>
       </c>
       <c r="O7" t="n">
-        <v>5.722976897823145</v>
+        <v>5.703385956661362</v>
       </c>
       <c r="P7" t="n">
-        <v>408.8853037699531</v>
+        <v>408.8874555659154</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28681,28 +28867,28 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3159968283471656</v>
+        <v>-0.3166138710477978</v>
       </c>
       <c r="J8" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="K8" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1398227246602612</v>
+        <v>0.1421304136388984</v>
       </c>
       <c r="M8" t="n">
-        <v>4.466250007156045</v>
+        <v>4.444907851786244</v>
       </c>
       <c r="N8" t="n">
-        <v>33.42016297082246</v>
+        <v>33.20392057908704</v>
       </c>
       <c r="O8" t="n">
-        <v>5.78101746847581</v>
+        <v>5.762284319528761</v>
       </c>
       <c r="P8" t="n">
-        <v>401.9988745207973</v>
+        <v>402.0053706705357</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28759,28 +28945,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1479800477516861</v>
+        <v>-0.1541839785492683</v>
       </c>
       <c r="J9" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="K9" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02943307676946805</v>
+        <v>0.03225416810930903</v>
       </c>
       <c r="M9" t="n">
-        <v>4.934749749666248</v>
+        <v>4.931386451148667</v>
       </c>
       <c r="N9" t="n">
-        <v>39.40299717860527</v>
+        <v>39.25808512284777</v>
       </c>
       <c r="O9" t="n">
-        <v>6.277180671177568</v>
+        <v>6.26562727289517</v>
       </c>
       <c r="P9" t="n">
-        <v>402.2589776543526</v>
+        <v>402.3246848791959</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28837,28 +29023,28 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03040485777179393</v>
+        <v>0.0251770028315391</v>
       </c>
       <c r="J10" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="K10" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001825728012630035</v>
+        <v>0.001267990951428821</v>
       </c>
       <c r="M10" t="n">
-        <v>4.216355447322053</v>
+        <v>4.21345016226925</v>
       </c>
       <c r="N10" t="n">
-        <v>27.6012572510045</v>
+        <v>27.49948729177414</v>
       </c>
       <c r="O10" t="n">
-        <v>5.253689870082217</v>
+        <v>5.243995355811649</v>
       </c>
       <c r="P10" t="n">
-        <v>403.5277157289366</v>
+        <v>403.5831786427371</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28896,7 +29082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K562"/>
+  <dimension ref="A1:K566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60801,6 +60987,234 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-36.528197763485906,174.71531695002514</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-36.52891948434636,174.7152903378493</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-36.52962989038872,174.71449745095018</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-36.53036564108271,174.7143560475925</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-36.53105150826375,174.71416811697753</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-36.53174990189537,174.7139881123166</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-36.53246456989403,174.71378813782965</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-36.5331545504716,174.71363487089056</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>-36.533846843637676,174.71367800017057</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-36.528199048406954,174.71534594078838</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-36.52892314139887,174.71537285079197</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-36.529636301848626,174.71455384740622</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-36.53037470613763,174.7144043418482</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-36.531054349201554,174.71418779442092</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-36.53175298849782,174.71401351147162</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-36.53246696361453,174.71380394342896</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-36.533154860254555,174.71363819917158</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-36.53384668317362,174.7136721962604</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-36.52820198393083,174.7154121735347</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-36.52892655130158,174.71544978854075</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-36.52963578641853,174.71454931357317</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-36.53037001027834,174.71437932455225</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-36.53105187330063,174.71417064536405</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-36.53175332399777,174.71401627224944</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-36.53247113599729,174.7138314934688</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-36.533155820581136,174.71364851684282</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-36.533846849809365,174.71367822339786</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-36.52820258190338,174.71542566539085</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-36.52892941755808,174.71551446085496</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-36.52964024928309,174.71458856993422</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-36.530374501969966,174.7144032541396</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-36.53105128606737,174.71416657795967</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-36.53175296165782,174.71401329060942</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-36.53247062068344,174.7138280908741</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-36.533155118406945,174.7136409727391</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-36.53384680660755,174.71367666080667</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K566"/>
+  <dimension ref="A1:K572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22452,6 +22452,240 @@
         <v>400.68</v>
       </c>
       <c r="K566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>460.21</v>
+      </c>
+      <c r="C567" t="n">
+        <v>470.99</v>
+      </c>
+      <c r="D567" t="n">
+        <v>398.68</v>
+      </c>
+      <c r="E567" t="n">
+        <v>401.08</v>
+      </c>
+      <c r="F567" t="n">
+        <v>398.53</v>
+      </c>
+      <c r="G567" t="n">
+        <v>395.41</v>
+      </c>
+      <c r="H567" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="I567" t="n">
+        <v>393.18</v>
+      </c>
+      <c r="J567" t="n">
+        <v>400.11</v>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>454.66</v>
+      </c>
+      <c r="C568" t="n">
+        <v>459.58</v>
+      </c>
+      <c r="D568" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="E568" t="n">
+        <v>399.46</v>
+      </c>
+      <c r="F568" t="n">
+        <v>397.78</v>
+      </c>
+      <c r="G568" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="H568" t="n">
+        <v>392.96</v>
+      </c>
+      <c r="I568" t="n">
+        <v>392.07</v>
+      </c>
+      <c r="J568" t="n">
+        <v>399.15</v>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>450.06</v>
+      </c>
+      <c r="C569" t="n">
+        <v>451.58</v>
+      </c>
+      <c r="D569" t="n">
+        <v>395.52</v>
+      </c>
+      <c r="E569" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="F569" t="n">
+        <v>395.78</v>
+      </c>
+      <c r="G569" t="n">
+        <v>392.44</v>
+      </c>
+      <c r="H569" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="I569" t="n">
+        <v>390.9</v>
+      </c>
+      <c r="J569" t="n">
+        <v>398.21</v>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>455.86</v>
+      </c>
+      <c r="C570" t="n">
+        <v>453.25</v>
+      </c>
+      <c r="D570" t="n">
+        <v>395.22</v>
+      </c>
+      <c r="E570" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="F570" t="n">
+        <v>394.32</v>
+      </c>
+      <c r="G570" t="n">
+        <v>390.92</v>
+      </c>
+      <c r="H570" t="n">
+        <v>390.78</v>
+      </c>
+      <c r="I570" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="J570" t="n">
+        <v>396.65</v>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>455.12</v>
+      </c>
+      <c r="C571" t="n">
+        <v>445.38</v>
+      </c>
+      <c r="D571" t="n">
+        <v>394.48</v>
+      </c>
+      <c r="E571" t="n">
+        <v>395.45</v>
+      </c>
+      <c r="F571" t="n">
+        <v>393.91</v>
+      </c>
+      <c r="G571" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="H571" t="n">
+        <v>390.34</v>
+      </c>
+      <c r="I571" t="n">
+        <v>388.04</v>
+      </c>
+      <c r="J571" t="n">
+        <v>396.25</v>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>452.37</v>
+      </c>
+      <c r="C572" t="n">
+        <v>445.38</v>
+      </c>
+      <c r="D572" t="n">
+        <v>394.43</v>
+      </c>
+      <c r="E572" t="n">
+        <v>395.38</v>
+      </c>
+      <c r="F572" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="G572" t="n">
+        <v>390.33</v>
+      </c>
+      <c r="H572" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="I572" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="J572" t="n">
+        <v>396.05</v>
+      </c>
+      <c r="K572" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22468,7 +22702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B576"/>
+  <dimension ref="A1:B582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28231,6 +28465,66 @@
       </c>
       <c r="B576" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -28399,28 +28693,28 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1015783243734737</v>
+        <v>0.1345181323502866</v>
       </c>
       <c r="J2" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K2" t="n">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001692084280673245</v>
+        <v>0.003008842950727453</v>
       </c>
       <c r="M2" t="n">
-        <v>14.00795935843887</v>
+        <v>14.08432645837795</v>
       </c>
       <c r="N2" t="n">
-        <v>334.9822609021711</v>
+        <v>334.115716238846</v>
       </c>
       <c r="O2" t="n">
-        <v>18.30252061608376</v>
+        <v>18.27883246377749</v>
       </c>
       <c r="P2" t="n">
-        <v>436.1382721020239</v>
+        <v>435.7871085650919</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28477,28 +28771,28 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1828378496938012</v>
+        <v>-0.1661403784244262</v>
       </c>
       <c r="J3" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K3" t="n">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002549474661560747</v>
+        <v>0.002151493889826939</v>
       </c>
       <c r="M3" t="n">
-        <v>21.97337336669043</v>
+        <v>21.82887984909562</v>
       </c>
       <c r="N3" t="n">
-        <v>691.7495630941373</v>
+        <v>685.7655826495093</v>
       </c>
       <c r="O3" t="n">
-        <v>26.30113235383863</v>
+        <v>26.18712627703752</v>
       </c>
       <c r="P3" t="n">
-        <v>451.4713385666681</v>
+        <v>451.2880402611514</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28555,28 +28849,28 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1967970856419625</v>
+        <v>-0.1961259331224739</v>
       </c>
       <c r="J4" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K4" t="n">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01560519556790774</v>
+        <v>0.01585683874101251</v>
       </c>
       <c r="M4" t="n">
-        <v>9.294279449063971</v>
+        <v>9.209368177796204</v>
       </c>
       <c r="N4" t="n">
-        <v>133.5951332159486</v>
+        <v>132.208626155143</v>
       </c>
       <c r="O4" t="n">
-        <v>11.55833609201379</v>
+        <v>11.49820099646649</v>
       </c>
       <c r="P4" t="n">
-        <v>400.8914648898224</v>
+        <v>400.8843160695484</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28633,28 +28927,28 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5105414161616315</v>
+        <v>-0.5199463899857197</v>
       </c>
       <c r="J5" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K5" t="n">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2276537260324583</v>
+        <v>0.2373882091781598</v>
       </c>
       <c r="M5" t="n">
-        <v>5.041819749947176</v>
+        <v>5.033859727737779</v>
       </c>
       <c r="N5" t="n">
-        <v>48.23190217618323</v>
+        <v>47.97779221978782</v>
       </c>
       <c r="O5" t="n">
-        <v>6.944919162681682</v>
+        <v>6.926600336369049</v>
       </c>
       <c r="P5" t="n">
-        <v>415.5907557105127</v>
+        <v>415.6914388829713</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28711,28 +29005,28 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5264140901197916</v>
+        <v>-0.5411944843834</v>
       </c>
       <c r="J6" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K6" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2964796235121451</v>
+        <v>0.3098550006368831</v>
       </c>
       <c r="M6" t="n">
-        <v>4.881503328796901</v>
+        <v>4.89617316216777</v>
       </c>
       <c r="N6" t="n">
-        <v>36.20150234577441</v>
+        <v>36.37251798998198</v>
       </c>
       <c r="O6" t="n">
-        <v>6.016768430459527</v>
+        <v>6.030963272146662</v>
       </c>
       <c r="P6" t="n">
-        <v>416.8834551540934</v>
+        <v>417.040807652011</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28789,28 +29083,28 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5011568753536099</v>
+        <v>-0.5078541381521462</v>
       </c>
       <c r="J7" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K7" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2976138032355655</v>
+        <v>0.3071744090520971</v>
       </c>
       <c r="M7" t="n">
-        <v>4.473332549692815</v>
+        <v>4.459492265062377</v>
       </c>
       <c r="N7" t="n">
-        <v>32.52861137064205</v>
+        <v>32.33217881012416</v>
       </c>
       <c r="O7" t="n">
-        <v>5.703385956661362</v>
+        <v>5.686139183147398</v>
       </c>
       <c r="P7" t="n">
-        <v>408.8874555659154</v>
+        <v>408.9588568638577</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28867,28 +29161,28 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3166138710477978</v>
+        <v>-0.3205954430702375</v>
       </c>
       <c r="J8" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K8" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1421304136388984</v>
+        <v>0.147894665605756</v>
       </c>
       <c r="M8" t="n">
-        <v>4.444907851786244</v>
+        <v>4.414192865149306</v>
       </c>
       <c r="N8" t="n">
-        <v>33.20392057908704</v>
+        <v>32.91346123038905</v>
       </c>
       <c r="O8" t="n">
-        <v>5.762284319528761</v>
+        <v>5.737025468863551</v>
       </c>
       <c r="P8" t="n">
-        <v>402.0053706705357</v>
+        <v>402.0478260547382</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28945,28 +29239,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1541839785492683</v>
+        <v>-0.1710367087600763</v>
       </c>
       <c r="J9" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K9" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03225416810930903</v>
+        <v>0.0395841837084886</v>
       </c>
       <c r="M9" t="n">
-        <v>4.931386451148667</v>
+        <v>4.966293349540054</v>
       </c>
       <c r="N9" t="n">
-        <v>39.25808512284777</v>
+        <v>39.56254362109667</v>
       </c>
       <c r="O9" t="n">
-        <v>6.26562727289517</v>
+        <v>6.289876280269483</v>
       </c>
       <c r="P9" t="n">
-        <v>402.3246848791959</v>
+        <v>402.5041489787345</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29023,28 +29317,28 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0251770028315391</v>
+        <v>0.01163230731293096</v>
       </c>
       <c r="J10" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="K10" t="n">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001267990951428821</v>
+        <v>0.0002726848128981052</v>
       </c>
       <c r="M10" t="n">
-        <v>4.21345016226925</v>
+        <v>4.239425062554013</v>
       </c>
       <c r="N10" t="n">
-        <v>27.49948729177414</v>
+        <v>27.6683585253397</v>
       </c>
       <c r="O10" t="n">
-        <v>5.243995355811649</v>
+        <v>5.26007210267499</v>
       </c>
       <c r="P10" t="n">
-        <v>403.5831786427371</v>
+        <v>403.7276393546134</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29082,7 +29376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K566"/>
+  <dimension ref="A1:K572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61215,6 +61509,348 @@
         </is>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-36.528201415608386,174.71539935069632</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-36.52892699606783,174.7154598238996</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-36.52964052585455,174.71459100272293</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-36.53037403238424,174.7144007524099</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-36.53105044489513,174.71416075167784</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-36.53175227723776,174.71400765862268</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-36.53246935733293,174.71381974902917</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-36.533154302645166,174.71363220826578</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-36.53384663071416,174.71367029882825</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-36.52819867281538,174.71533746656522</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-36.52892135735744,174.7153325978557</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-36.52963897956801,174.7145774012226</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-36.530370724865975,174.7143831315319</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-36.53104925455657,174.7141525069396</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-36.53175072051656,174.71399484861405</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-36.53246799424355,174.71381074861782</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-36.53315315644712,174.71361989362637</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>-36.5338463344719,174.7136595839173</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-36.52819639948504,174.71528617521565</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-36.52891740375441,174.7152433946776</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-36.529636553277875,174.7145560590321</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-36.530366110669384,174.7143585493217</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-36.531046080317594,174.71413052097208</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-36.53174829149193,174.71397486058424</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-36.532466614530435,174.7138016384457</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-36.53315194829104,174.7136069133311</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>-36.533846044400434,174.71364909223365</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-36.52819926585443,174.71535084691763</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-36.52891822907458,174.7152620158405</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-36.529636176133984,174.71455274159328</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-36.530364028154196,174.71434745469676</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-36.53104376312055,174.71411447121682</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-36.53174625164542,174.7139580750573</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-36.532464370417216,174.7137868206964</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-36.533149686866864,174.71358261688187</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>-36.53384556300319,174.71363168050345</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-36.528198900147196,174.7153425957003</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-36.528914339665995,174.71517426221894</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-36.52963524584532,174.7145445585776</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-36.53036253772601,174.7143395144263</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-36.53104311240043,174.71410996409392</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-36.531745513542475,174.7139520013471</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-36.53246363900214,174.71378199120795</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-36.53314899501463,174.71357518372187</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>-36.533845439567585,174.71362721595725</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-36.52819754109501,174.7153119323931</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-36.528914339665995,174.71517426221894</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-36.52963518298797,174.71454400567114</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-36.530362394808215,174.71433875303052</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-36.53104316001413,174.7141102938834</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-36.53174545986226,174.71395155962273</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-36.53246282447148,174.71377661291405</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-36.533148561315976,174.7135705241291</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>-36.53384537784973,174.71362498368416</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K572"/>
+  <dimension ref="A1:K575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22662,7 +22662,7 @@
         <v>452.37</v>
       </c>
       <c r="C572" t="n">
-        <v>445.38</v>
+        <v>443.75</v>
       </c>
       <c r="D572" t="n">
         <v>394.43</v>
@@ -22688,6 +22688,123 @@
       <c r="K572" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>452.37</v>
+      </c>
+      <c r="C573" t="n">
+        <v>443.75</v>
+      </c>
+      <c r="D573" t="n">
+        <v>394.43</v>
+      </c>
+      <c r="E573" t="n">
+        <v>394.53</v>
+      </c>
+      <c r="F573" t="n">
+        <v>393.27</v>
+      </c>
+      <c r="G573" t="n">
+        <v>389.51</v>
+      </c>
+      <c r="H573" t="n">
+        <v>388.57</v>
+      </c>
+      <c r="I573" t="n">
+        <v>386.2</v>
+      </c>
+      <c r="J573" t="n">
+        <v>395.26</v>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>446.67</v>
+      </c>
+      <c r="C574" t="n">
+        <v>446.31</v>
+      </c>
+      <c r="D574" t="n">
+        <v>390.23</v>
+      </c>
+      <c r="E574" t="n">
+        <v>390.78</v>
+      </c>
+      <c r="F574" t="n">
+        <v>390.86</v>
+      </c>
+      <c r="G574" t="n">
+        <v>386.82</v>
+      </c>
+      <c r="H574" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="I574" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="J574" t="n">
+        <v>393.56</v>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>451.67</v>
+      </c>
+      <c r="C575" t="n">
+        <v>449.48</v>
+      </c>
+      <c r="D575" t="n">
+        <v>390.23</v>
+      </c>
+      <c r="E575" t="n">
+        <v>390.78</v>
+      </c>
+      <c r="F575" t="n">
+        <v>390.86</v>
+      </c>
+      <c r="G575" t="n">
+        <v>386.41</v>
+      </c>
+      <c r="H575" t="n">
+        <v>385.82</v>
+      </c>
+      <c r="I575" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="J575" t="n">
+        <v>393.63</v>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -22702,7 +22819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B582"/>
+  <dimension ref="A1:B585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28525,6 +28642,36 @@
       </c>
       <c r="B582" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -28693,28 +28840,28 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1345181323502866</v>
+        <v>0.1457011689917063</v>
       </c>
       <c r="J2" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K2" t="n">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003008842950727453</v>
+        <v>0.003561723945071149</v>
       </c>
       <c r="M2" t="n">
-        <v>14.08432645837795</v>
+        <v>14.08564868295377</v>
       </c>
       <c r="N2" t="n">
-        <v>334.115716238846</v>
+        <v>332.9998325859398</v>
       </c>
       <c r="O2" t="n">
-        <v>18.27883246377749</v>
+        <v>18.24828300377709</v>
       </c>
       <c r="P2" t="n">
-        <v>435.7871085650919</v>
+        <v>435.6673248038542</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28771,28 +28918,28 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1661403784244262</v>
+        <v>-0.1670567803869006</v>
       </c>
       <c r="J3" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K3" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002151493889826939</v>
+        <v>0.002200486422609171</v>
       </c>
       <c r="M3" t="n">
-        <v>21.82887984909562</v>
+        <v>21.72579893718521</v>
       </c>
       <c r="N3" t="n">
-        <v>685.7655826495093</v>
+        <v>682.1286528742521</v>
       </c>
       <c r="O3" t="n">
-        <v>26.18712627703752</v>
+        <v>26.11759278483092</v>
       </c>
       <c r="P3" t="n">
-        <v>451.2880402611514</v>
+        <v>451.2981039875828</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28849,28 +28996,28 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1961259331224739</v>
+        <v>-0.2002756278294765</v>
       </c>
       <c r="J4" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K4" t="n">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01585683874101251</v>
+        <v>0.01669860227193787</v>
       </c>
       <c r="M4" t="n">
-        <v>9.209368177796204</v>
+        <v>9.182880626229306</v>
       </c>
       <c r="N4" t="n">
-        <v>132.208626155143</v>
+        <v>131.6161509745062</v>
       </c>
       <c r="O4" t="n">
-        <v>11.49820099646649</v>
+        <v>11.47240824650632</v>
       </c>
       <c r="P4" t="n">
-        <v>400.8843160695484</v>
+        <v>400.9289644567784</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28927,28 +29074,28 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5199463899857197</v>
+        <v>-0.530023332063861</v>
       </c>
       <c r="J5" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K5" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2373882091781598</v>
+        <v>0.2445990542060211</v>
       </c>
       <c r="M5" t="n">
-        <v>5.033859727737779</v>
+        <v>5.056051755373732</v>
       </c>
       <c r="N5" t="n">
-        <v>47.97779221978782</v>
+        <v>48.22961817062762</v>
       </c>
       <c r="O5" t="n">
-        <v>6.926600336369049</v>
+        <v>6.944754723575745</v>
       </c>
       <c r="P5" t="n">
-        <v>415.6914388829713</v>
+        <v>415.7997888789803</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29005,28 +29152,28 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5411944843834</v>
+        <v>-0.5523966463347793</v>
       </c>
       <c r="J6" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K6" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3098550006368831</v>
+        <v>0.3175086899221038</v>
       </c>
       <c r="M6" t="n">
-        <v>4.89617316216777</v>
+        <v>4.921067660414339</v>
       </c>
       <c r="N6" t="n">
-        <v>36.37251798998198</v>
+        <v>36.79822037032493</v>
       </c>
       <c r="O6" t="n">
-        <v>6.030963272146662</v>
+        <v>6.066153671835633</v>
       </c>
       <c r="P6" t="n">
-        <v>417.040807652011</v>
+        <v>417.1606101552404</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29083,28 +29230,28 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5078541381521462</v>
+        <v>-0.5158616667289531</v>
       </c>
       <c r="J7" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K7" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3071744090520971</v>
+        <v>0.3142153124110157</v>
       </c>
       <c r="M7" t="n">
-        <v>4.459492265062377</v>
+        <v>4.475961516118481</v>
       </c>
       <c r="N7" t="n">
-        <v>32.33217881012416</v>
+        <v>32.48308529714928</v>
       </c>
       <c r="O7" t="n">
-        <v>5.686139183147398</v>
+        <v>5.699393414842432</v>
       </c>
       <c r="P7" t="n">
-        <v>408.9588568638577</v>
+        <v>409.0445915918044</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29161,28 +29308,28 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3205954430702375</v>
+        <v>-0.3273689413400606</v>
       </c>
       <c r="J8" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K8" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L8" t="n">
-        <v>0.147894665605756</v>
+        <v>0.1538276299554979</v>
       </c>
       <c r="M8" t="n">
-        <v>4.414192865149306</v>
+        <v>4.41708958562069</v>
       </c>
       <c r="N8" t="n">
-        <v>32.91346123038905</v>
+        <v>32.97082083694934</v>
       </c>
       <c r="O8" t="n">
-        <v>5.737025468863551</v>
+        <v>5.742022364720408</v>
       </c>
       <c r="P8" t="n">
-        <v>402.0478260547382</v>
+        <v>402.1203489496644</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29239,28 +29386,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1710367087600763</v>
+        <v>-0.1852827520449605</v>
       </c>
       <c r="J9" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K9" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0395841837084886</v>
+        <v>0.0455425114071516</v>
       </c>
       <c r="M9" t="n">
-        <v>4.966293349540054</v>
+        <v>5.015881141360129</v>
       </c>
       <c r="N9" t="n">
-        <v>39.56254362109667</v>
+        <v>40.35291272830246</v>
       </c>
       <c r="O9" t="n">
-        <v>6.289876280269483</v>
+        <v>6.35239425164264</v>
       </c>
       <c r="P9" t="n">
-        <v>402.5041489787345</v>
+        <v>402.6565458750407</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29317,28 +29464,28 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01163230731293096</v>
+        <v>0.001427655062500791</v>
       </c>
       <c r="J10" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K10" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002726848128981052</v>
+        <v>4.080170215470247e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>4.239425062554013</v>
+        <v>4.27073524839466</v>
       </c>
       <c r="N10" t="n">
-        <v>27.6683585253397</v>
+        <v>28.03319707782296</v>
       </c>
       <c r="O10" t="n">
-        <v>5.26007210267499</v>
+        <v>5.294638521922244</v>
       </c>
       <c r="P10" t="n">
-        <v>403.7276393546134</v>
+        <v>403.8369746067075</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29376,7 +29523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K572"/>
+  <dimension ref="A1:K575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61807,7 +61954,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>-36.528914339665995,174.71517426221894</t>
+          <t>-36.52891353410058,174.71515608707318</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -61848,6 +61995,177 @@
       <c r="K572" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-36.52819754109501,174.7153119323931</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-36.52891353410058,174.71515608707318</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-36.52963518298797,174.71454400567114</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>-36.5303606593774,174.71432950751054</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-36.53104209664188,174.71410292858513</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-36.53174435941725,174.71394250427318</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-36.53246069671675,174.71376256349376</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-36.533147095000125,174.71355477026808</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>-36.533845134063746,174.71361616620547</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-36.528194724125235,174.7152483757224</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-36.52891479928182,174.7151846320875</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-36.52962990296023,174.7144975615315</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>-36.53035300305631,174.71428871845632</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-36.53103827167226,174.71407643549892</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-36.531740749415974,174.71391279831096</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-36.53245687340327,174.7137373184435</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-36.53314391453318,174.71352059992347</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>-36.53384460945879,174.71359719188433</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-36.52819719515318,174.71530412718775</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>-36.52891636592252,174.7152199788444</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>-36.52962990296023,174.7144975615315</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-36.53035300305631,174.71428871845632</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-36.53103827167226,174.71407643549892</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-36.53174019919207,174.71390827063664</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-36.53245612536306,174.71373237919477</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-36.53314374931387,174.7135188248407</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>-36.533844631060234,174.7135979731799</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
